--- a/Result/profitability/8071.xlsx
+++ b/Result/profitability/8071.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.19</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.25375</v>
+        <v>-0.23875</v>
       </c>
       <c r="N2" t="n">
-        <v>15.64125</v>
+        <v>15.90125</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>-0.04</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.2025</v>
+        <v>-0.26875</v>
       </c>
       <c r="N3" t="n">
-        <v>15.42</v>
+        <v>15.32125</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>-0.27</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.26125</v>
+        <v>-0.2</v>
       </c>
       <c r="N4" t="n">
-        <v>13.82375</v>
+        <v>14.03</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.15</v>
+        <v>-0.12875</v>
       </c>
       <c r="N5" t="n">
-        <v>14.38875</v>
+        <v>14.4875</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.16</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.06749999999999998</v>
+        <v>-0.17875</v>
       </c>
       <c r="N6" t="n">
-        <v>14.535</v>
+        <v>14.41</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1149,7 +1149,7 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.29</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.10125</v>
+        <v>-0.08749999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>15.5475</v>
+        <v>15.4825</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.08</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.03624999999999999</v>
+        <v>-0.02874999999999998</v>
       </c>
       <c r="N8" t="n">
-        <v>15.19125</v>
+        <v>15.465</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,7 +1518,7 @@
         <v>0.37</v>
       </c>
       <c r="M9" t="n">
-        <v>0.05875000000000001</v>
+        <v>0.05875000000000002</v>
       </c>
       <c r="N9" t="n">
         <v>14.7875</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>8071</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>628</v>
+      </c>
+      <c r="D75" t="n">
+        <v>521</v>
+      </c>
+      <c r="E75" t="n">
+        <v>107</v>
+      </c>
+      <c r="F75" t="n">
+        <v>16.98</v>
+      </c>
+      <c r="G75" t="n">
+        <v>2</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>0.29%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-8</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-20</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.27125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>16.43</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.1538461538461539</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>2.190000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.1480730223123734</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>0.7899999999999991</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.04879555281037673</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
